--- a/tracking_forms/001_equipment_release_form--tracking_forms.xlsx
+++ b/tracking_forms/001_equipment_release_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -715,8 +715,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -744,12 +744,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'employee_1',_'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'employee_1', 'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'employee_2',_'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'employee_2', 'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_1',_'label':_'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_1', 'label': 'Laptop'}</t>
+          <t>Laptop</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_2',_'label':_'mobile_phone'}</t>
+          <t>mobile_phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'equipment_2', 'label': 'Mobile Phone'}</t>
+          <t>Mobile Phone</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'manager_1',_'label':_'john_smith'}</t>
+          <t>john_smith</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'manager_1', 'label': 'John Smith'}</t>
+          <t>John Smith</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'manager_2',_'label':_'jane_smith'}</t>
+          <t>jane_smith</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'manager_2', 'label': 'Jane Smith'}</t>
+          <t>Jane Smith</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'department_1',_'label':_'sales_and_marketing'}</t>
+          <t>sales_and_marketing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'department_1', 'label': 'Sales and Marketing'}</t>
+          <t>Sales and Marketing</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'department_2',_'label':_'customer_support'}</t>
+          <t>customer_support</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'department_2', 'label': 'Customer Support'}</t>
+          <t>Customer Support</t>
         </is>
       </c>
     </row>
